--- a/DATA/DataMaster.xlsx
+++ b/DATA/DataMaster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\University\4th year\Thesis\Thesis\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvtruc\Downloads\HuynhHoangMyDung\Thesis\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7FE43F-5A94-421D-810D-36606E9A74D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FAF915-0C0B-4576-9F2F-79AF75232943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MachineMaster" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="235">
   <si>
     <t>MachineID</t>
   </si>
@@ -691,12 +691,6 @@
   </si>
   <si>
     <t>_fixed_instance</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>done</t>
   </si>
   <si>
     <t>valid1</t>
@@ -758,10 +752,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0\ _B_F_-;\-* #,##0\ _B_F_-;_-* &quot;-&quot;\ _B_F_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0\ _B_F_-;\-* #,##0\ _B_F_-;_-* &quot;-&quot;\ _B_F_-;_-@_-"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -1121,10 +1115,10 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1151,42 +1145,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1230,7 +1224,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1319,7 +1313,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1458,10 +1452,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1653,7 +1647,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1665,25 +1659,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2082,25 +2076,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="63" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="52" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="63" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" style="52" customWidth="1"/>
-    <col min="5" max="5" width="28.44140625" style="52" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="52" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="52" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" style="52" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" style="52" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" style="52" customWidth="1"/>
-    <col min="13" max="13" width="22.5546875" style="52" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="52" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="52"/>
+    <col min="1" max="1" width="12.5703125" style="63" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" style="63" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" style="52" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="52" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="52" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" style="52" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="52" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" style="52" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="52" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" style="52" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="52" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
@@ -2138,7 +2132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="66">
         <v>1</v>
       </c>
@@ -2178,7 +2172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="78">
         <v>2</v>
       </c>
@@ -2218,7 +2212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="81">
         <v>3</v>
       </c>
@@ -2258,7 +2252,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="74">
         <v>4</v>
       </c>
@@ -2298,7 +2292,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="78">
         <v>5</v>
       </c>
@@ -2338,7 +2332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>6</v>
       </c>
@@ -2378,7 +2372,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="57">
         <v>7</v>
       </c>
@@ -2418,7 +2412,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>8</v>
       </c>
@@ -2458,7 +2452,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>9</v>
       </c>
@@ -2498,7 +2492,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>10</v>
       </c>
@@ -2538,7 +2532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>11</v>
       </c>
@@ -2578,7 +2572,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>12</v>
       </c>
@@ -2598,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="81">
         <v>13</v>
       </c>
@@ -2619,7 +2613,7 @@
       </c>
       <c r="I14" s="53"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="69">
         <v>14</v>
       </c>
@@ -2639,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="54">
         <v>15</v>
       </c>
@@ -2659,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="74">
         <v>16</v>
       </c>
@@ -2685,7 +2679,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="78">
         <v>17</v>
       </c>
@@ -2711,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="81">
         <v>18</v>
       </c>
@@ -2737,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>19</v>
       </c>
@@ -2763,7 +2757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="74">
         <v>20</v>
       </c>
@@ -2789,7 +2783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="78">
         <v>21</v>
       </c>
@@ -2815,7 +2809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="81">
         <v>22</v>
       </c>
@@ -2841,7 +2835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="69">
         <v>23</v>
       </c>
@@ -2867,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="54">
         <v>24</v>
       </c>
@@ -2893,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="74">
         <v>25</v>
       </c>
@@ -2919,7 +2913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="78">
         <v>26</v>
       </c>
@@ -2945,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="81">
         <v>27</v>
       </c>
@@ -2971,7 +2965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="69">
         <v>28</v>
       </c>
@@ -2998,7 +2992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="54">
         <v>29</v>
       </c>
@@ -3018,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>30</v>
       </c>
@@ -3051,19 +3045,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3BC26D-AF97-4798-83B8-6ABF36AF857F}">
   <dimension ref="B1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B1" s="186" t="s">
         <v>186</v>
       </c>
@@ -3083,7 +3077,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="155" t="s">
         <v>191</v>
       </c>
@@ -3103,8 +3097,12 @@
       <c r="G2" s="155">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <f>F2*1.5</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="194" t="s">
         <v>191</v>
       </c>
@@ -3124,8 +3122,12 @@
       <c r="G3" s="194">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <f t="shared" ref="I3:I24" si="0">F3*1.5</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="145" t="s">
         <v>192</v>
       </c>
@@ -3145,8 +3147,12 @@
       <c r="G4" s="145">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="193" t="s">
         <v>192</v>
       </c>
@@ -3166,8 +3172,12 @@
       <c r="G5" s="193">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="189" t="s">
         <v>193</v>
       </c>
@@ -3187,8 +3197,12 @@
       <c r="G6" s="189">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="190" t="s">
         <v>194</v>
       </c>
@@ -3208,8 +3222,12 @@
       <c r="G7" s="190">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="191" t="s">
         <v>194</v>
       </c>
@@ -3229,8 +3247,12 @@
       <c r="G8" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="191" t="s">
         <v>194</v>
       </c>
@@ -3250,8 +3272,12 @@
       <c r="G9" s="191">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="191" t="s">
         <v>194</v>
       </c>
@@ -3271,8 +3297,12 @@
       <c r="G10" s="191">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="191" t="s">
         <v>194</v>
       </c>
@@ -3292,8 +3322,12 @@
       <c r="G11" s="191">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="191" t="s">
         <v>194</v>
       </c>
@@ -3313,8 +3347,12 @@
       <c r="G12" s="191">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="191" t="s">
         <v>194</v>
       </c>
@@ -3334,8 +3372,12 @@
       <c r="G13" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="191" t="s">
         <v>194</v>
       </c>
@@ -3355,8 +3397,12 @@
       <c r="G14" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="191" t="s">
         <v>194</v>
       </c>
@@ -3376,8 +3422,12 @@
       <c r="G15" s="191">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="191" t="s">
         <v>194</v>
       </c>
@@ -3397,8 +3447,12 @@
       <c r="G16" s="191">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="191" t="s">
         <v>194</v>
       </c>
@@ -3418,8 +3472,12 @@
       <c r="G17" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="191" t="s">
         <v>194</v>
       </c>
@@ -3439,8 +3497,12 @@
       <c r="G18" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="191" t="s">
         <v>194</v>
       </c>
@@ -3460,8 +3522,12 @@
       <c r="G19" s="191">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="191" t="s">
         <v>194</v>
       </c>
@@ -3481,8 +3547,12 @@
       <c r="G20" s="191">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="191" t="s">
         <v>194</v>
       </c>
@@ -3502,8 +3572,12 @@
       <c r="G21" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="191" t="s">
         <v>194</v>
       </c>
@@ -3523,8 +3597,12 @@
       <c r="G22" s="191">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="191" t="s">
         <v>194</v>
       </c>
@@ -3544,8 +3622,12 @@
       <c r="G23" s="191">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="192" t="s">
         <v>194</v>
       </c>
@@ -3565,8 +3647,12 @@
       <c r="G24" s="192">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="213" t="s">
         <v>186</v>
       </c>
@@ -3577,7 +3663,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="255" t="s">
         <v>191</v>
       </c>
@@ -3588,7 +3674,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="256"/>
       <c r="C30" s="215" t="s">
         <v>176</v>
@@ -3597,7 +3683,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="252" t="s">
         <v>192</v>
       </c>
@@ -3608,7 +3694,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="254"/>
       <c r="C32" s="218" t="s">
         <v>179</v>
@@ -3617,7 +3703,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B33" s="223" t="s">
         <v>193</v>
       </c>
@@ -3628,7 +3714,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="252" t="s">
         <v>194</v>
       </c>
@@ -3639,7 +3725,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="253"/>
       <c r="C35" s="221" t="s">
         <v>154</v>
@@ -3648,7 +3734,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="253"/>
       <c r="C36" s="221" t="s">
         <v>155</v>
@@ -3657,7 +3743,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="253"/>
       <c r="C37" s="221" t="s">
         <v>156</v>
@@ -3666,7 +3752,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="253"/>
       <c r="C38" s="221" t="s">
         <v>157</v>
@@ -3675,7 +3761,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="253"/>
       <c r="C39" s="221" t="s">
         <v>158</v>
@@ -3684,7 +3770,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="253"/>
       <c r="C40" s="221" t="s">
         <v>159</v>
@@ -3693,7 +3779,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="253"/>
       <c r="C41" s="221" t="s">
         <v>160</v>
@@ -3702,7 +3788,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="253"/>
       <c r="C42" s="221" t="s">
         <v>161</v>
@@ -3711,7 +3797,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="253"/>
       <c r="C43" s="221" t="s">
         <v>162</v>
@@ -3720,7 +3806,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="253"/>
       <c r="C44" s="221" t="s">
         <v>163</v>
@@ -3729,7 +3815,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="253"/>
       <c r="C45" s="221" t="s">
         <v>164</v>
@@ -3740,7 +3826,7 @@
       <c r="I45" s="196"/>
       <c r="J45" s="196"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="253"/>
       <c r="C46" s="221" t="s">
         <v>165</v>
@@ -3749,7 +3835,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="253"/>
       <c r="C47" s="221" t="s">
         <v>166</v>
@@ -3758,7 +3844,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="253"/>
       <c r="C48" s="221" t="s">
         <v>167</v>
@@ -3767,7 +3853,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="253"/>
       <c r="C49" s="221" t="s">
         <v>169</v>
@@ -3776,7 +3862,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="253"/>
       <c r="C50" s="221" t="s">
         <v>170</v>
@@ -3785,7 +3871,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="254"/>
       <c r="C51" s="222" t="s">
         <v>168</v>
@@ -3806,18 +3892,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA1E3C2B-EB2A-4B5B-9A38-8DCE83FFCF73}">
-  <dimension ref="A1:H224"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G224"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="195" t="s">
         <v>187</v>
       </c>
@@ -3840,7 +3925,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="197" t="s">
         <v>216</v>
       </c>
@@ -3864,7 +3949,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="197" t="s">
         <v>216</v>
       </c>
@@ -3888,7 +3973,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="197" t="s">
         <v>216</v>
       </c>
@@ -3912,7 +3997,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="202">
         <v>2</v>
       </c>
@@ -3938,7 +4023,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="202">
         <v>2</v>
       </c>
@@ -3964,7 +4049,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="202">
         <v>2</v>
       </c>
@@ -3990,7 +4075,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="202">
         <v>2</v>
       </c>
@@ -4016,7 +4101,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="199">
         <v>3</v>
       </c>
@@ -4042,7 +4127,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="199">
         <v>3</v>
       </c>
@@ -4068,7 +4153,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="199">
         <v>3</v>
       </c>
@@ -4094,7 +4179,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="202">
         <v>4</v>
       </c>
@@ -4120,7 +4205,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="202">
         <v>4</v>
       </c>
@@ -4146,7 +4231,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="202">
         <v>4</v>
       </c>
@@ -4172,7 +4257,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="202">
         <v>4</v>
       </c>
@@ -4198,7 +4283,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="199">
         <v>5</v>
       </c>
@@ -4224,7 +4309,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="199">
         <v>5</v>
       </c>
@@ -4250,7 +4335,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="202">
         <v>6</v>
       </c>
@@ -4276,7 +4361,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="202">
         <v>6</v>
       </c>
@@ -4302,7 +4387,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="202">
         <v>6</v>
       </c>
@@ -4328,7 +4413,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="202">
         <v>6</v>
       </c>
@@ -4354,7 +4439,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="199">
         <v>7</v>
       </c>
@@ -4380,7 +4465,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="199">
         <v>7</v>
       </c>
@@ -4406,7 +4491,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="199">
         <v>7</v>
       </c>
@@ -4432,7 +4517,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="199">
         <v>7</v>
       </c>
@@ -4458,7 +4543,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="202">
         <v>8</v>
       </c>
@@ -4484,7 +4569,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="202">
         <v>8</v>
       </c>
@@ -4510,7 +4595,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="202">
         <v>8</v>
       </c>
@@ -4536,7 +4621,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="199">
         <v>9</v>
       </c>
@@ -4562,7 +4647,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="199">
         <v>9</v>
       </c>
@@ -4588,7 +4673,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="202">
         <v>10</v>
       </c>
@@ -4614,7 +4699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="202">
         <v>10</v>
       </c>
@@ -4640,7 +4725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="202">
         <v>10</v>
       </c>
@@ -4666,7 +4751,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="202">
         <v>10</v>
       </c>
@@ -4692,7 +4777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="202">
         <v>10</v>
       </c>
@@ -4718,7 +4803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="199">
         <v>11</v>
       </c>
@@ -4743,11 +4828,8 @@
         <f t="shared" si="0"/>
         <v>1470</v>
       </c>
-      <c r="H36" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="199">
         <v>11</v>
       </c>
@@ -4773,7 +4855,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="202">
         <v>12</v>
       </c>
@@ -4798,11 +4880,8 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="202">
         <v>12</v>
       </c>
@@ -4828,7 +4907,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="202">
         <v>12</v>
       </c>
@@ -4854,7 +4933,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="199">
         <v>13</v>
       </c>
@@ -4879,11 +4958,8 @@
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="H41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="200">
         <v>13</v>
       </c>
@@ -4909,7 +4985,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="202">
         <v>14</v>
       </c>
@@ -4934,11 +5010,8 @@
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
-      <c r="H43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="202">
         <v>14</v>
       </c>
@@ -4964,7 +5037,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="202">
         <v>14</v>
       </c>
@@ -4990,7 +5063,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="199">
         <v>15</v>
       </c>
@@ -5015,11 +5088,8 @@
         <f t="shared" si="0"/>
         <v>375</v>
       </c>
-      <c r="H46" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="199">
         <v>15</v>
       </c>
@@ -5045,7 +5115,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="199">
         <v>15</v>
       </c>
@@ -5071,7 +5141,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="202">
         <v>16</v>
       </c>
@@ -5097,7 +5167,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="202">
         <v>16</v>
       </c>
@@ -5123,7 +5193,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="202">
         <v>16</v>
       </c>
@@ -5149,7 +5219,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="199">
         <v>17</v>
       </c>
@@ -5175,7 +5245,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="199">
         <v>17</v>
       </c>
@@ -5201,7 +5271,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="199">
         <v>17</v>
       </c>
@@ -5227,7 +5297,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="199">
         <v>17</v>
       </c>
@@ -5253,7 +5323,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="202">
         <v>18</v>
       </c>
@@ -5279,7 +5349,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="202">
         <v>18</v>
       </c>
@@ -5305,7 +5375,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="202">
         <v>18</v>
       </c>
@@ -5331,7 +5401,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="199">
         <v>19</v>
       </c>
@@ -5357,7 +5427,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="199">
         <v>19</v>
       </c>
@@ -5383,7 +5453,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="199">
         <v>19</v>
       </c>
@@ -5409,7 +5479,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="199">
         <v>19</v>
       </c>
@@ -5435,7 +5505,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="202">
         <v>20</v>
       </c>
@@ -5461,7 +5531,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="202">
         <v>20</v>
       </c>
@@ -5487,7 +5557,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="202">
         <v>20</v>
       </c>
@@ -5513,7 +5583,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="202">
         <v>20</v>
       </c>
@@ -5539,7 +5609,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="199">
         <v>21</v>
       </c>
@@ -5565,7 +5635,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="199">
         <v>21</v>
       </c>
@@ -5591,7 +5661,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="199">
         <v>21</v>
       </c>
@@ -5617,7 +5687,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="199">
         <v>21</v>
       </c>
@@ -5643,7 +5713,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="202">
         <v>22</v>
       </c>
@@ -5669,7 +5739,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="202">
         <v>22</v>
       </c>
@@ -5695,7 +5765,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="202">
         <v>22</v>
       </c>
@@ -5721,7 +5791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="202">
         <v>22</v>
       </c>
@@ -5747,7 +5817,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="202">
         <v>22</v>
       </c>
@@ -5773,7 +5843,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="199">
         <v>23</v>
       </c>
@@ -5799,7 +5869,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="199">
         <v>23</v>
       </c>
@@ -5825,7 +5895,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="199">
         <v>23</v>
       </c>
@@ -5851,7 +5921,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="199">
         <v>23</v>
       </c>
@@ -5877,7 +5947,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="202">
         <v>24</v>
       </c>
@@ -5903,7 +5973,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="202">
         <v>24</v>
       </c>
@@ -5929,7 +5999,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="202">
         <v>24</v>
       </c>
@@ -5955,7 +6025,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="202">
         <v>24</v>
       </c>
@@ -5981,7 +6051,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="202">
         <v>24</v>
       </c>
@@ -6007,7 +6077,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="199">
         <v>25</v>
       </c>
@@ -6033,7 +6103,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="199">
         <v>25</v>
       </c>
@@ -6059,7 +6129,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="199">
         <v>25</v>
       </c>
@@ -6085,7 +6155,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="199">
         <v>25</v>
       </c>
@@ -6111,7 +6181,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="202">
         <v>26</v>
       </c>
@@ -6137,7 +6207,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="202">
         <v>26</v>
       </c>
@@ -6163,7 +6233,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="202">
         <v>26</v>
       </c>
@@ -6189,7 +6259,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="199">
         <v>27</v>
       </c>
@@ -6215,7 +6285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="199">
         <v>27</v>
       </c>
@@ -6241,7 +6311,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="199">
         <v>27</v>
       </c>
@@ -6267,7 +6337,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="199">
         <v>27</v>
       </c>
@@ -6293,7 +6363,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="202">
         <v>28</v>
       </c>
@@ -6319,7 +6389,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="202">
         <v>28</v>
       </c>
@@ -6345,7 +6415,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="202">
         <v>28</v>
       </c>
@@ -6371,7 +6441,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="199">
         <v>29</v>
       </c>
@@ -6397,7 +6467,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="199">
         <v>29</v>
       </c>
@@ -6423,7 +6493,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="199">
         <v>29</v>
       </c>
@@ -6449,7 +6519,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="199">
         <v>29</v>
       </c>
@@ -6475,7 +6545,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="203">
         <v>30</v>
       </c>
@@ -6501,7 +6571,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="202">
         <v>30</v>
       </c>
@@ -6527,7 +6597,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="202">
         <v>30</v>
       </c>
@@ -6553,7 +6623,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="202">
         <v>30</v>
       </c>
@@ -6579,7 +6649,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="199">
         <v>31</v>
       </c>
@@ -6605,7 +6675,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="199">
         <v>31</v>
       </c>
@@ -6631,7 +6701,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="199">
         <v>31</v>
       </c>
@@ -6657,7 +6727,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="199">
         <v>31</v>
       </c>
@@ -6683,7 +6753,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="199">
         <v>31</v>
       </c>
@@ -6709,7 +6779,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="202">
         <v>32</v>
       </c>
@@ -6735,7 +6805,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="202">
         <v>32</v>
       </c>
@@ -6761,7 +6831,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="202">
         <v>32</v>
       </c>
@@ -6787,7 +6857,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="202">
         <v>32</v>
       </c>
@@ -6813,7 +6883,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="199">
         <v>33</v>
       </c>
@@ -6839,7 +6909,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="199">
         <v>33</v>
       </c>
@@ -6865,7 +6935,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="202">
         <v>34</v>
       </c>
@@ -6891,7 +6961,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="202">
         <v>34</v>
       </c>
@@ -6917,7 +6987,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="202">
         <v>34</v>
       </c>
@@ -6943,7 +7013,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="202">
         <v>34</v>
       </c>
@@ -6969,7 +7039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="202">
         <v>34</v>
       </c>
@@ -6995,7 +7065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="199">
         <v>35</v>
       </c>
@@ -7021,7 +7091,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="199">
         <v>35</v>
       </c>
@@ -7047,7 +7117,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="199">
         <v>35</v>
       </c>
@@ -7073,7 +7143,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="199">
         <v>35</v>
       </c>
@@ -7099,7 +7169,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="202">
         <v>36</v>
       </c>
@@ -7125,7 +7195,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="202">
         <v>36</v>
       </c>
@@ -7151,7 +7221,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="202">
         <v>36</v>
       </c>
@@ -7177,7 +7247,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="202">
         <v>36</v>
       </c>
@@ -7203,7 +7273,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="199">
         <v>37</v>
       </c>
@@ -7229,7 +7299,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="199">
         <v>37</v>
       </c>
@@ -7255,7 +7325,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="199">
         <v>37</v>
       </c>
@@ -7281,7 +7351,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="202">
         <v>38</v>
       </c>
@@ -7307,7 +7377,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="202">
         <v>38</v>
       </c>
@@ -7333,7 +7403,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="202">
         <v>38</v>
       </c>
@@ -7359,7 +7429,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="199">
         <v>39</v>
       </c>
@@ -7385,7 +7455,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="199">
         <v>39</v>
       </c>
@@ -7411,7 +7481,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="199">
         <v>39</v>
       </c>
@@ -7437,7 +7507,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="202">
         <v>40</v>
       </c>
@@ -7463,7 +7533,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="202">
         <v>40</v>
       </c>
@@ -7489,7 +7559,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="202">
         <v>40</v>
       </c>
@@ -7515,7 +7585,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="199">
         <v>41</v>
       </c>
@@ -7541,7 +7611,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="199">
         <v>41</v>
       </c>
@@ -7567,7 +7637,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="199">
         <v>41</v>
       </c>
@@ -7593,7 +7663,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="202">
         <v>42</v>
       </c>
@@ -7619,7 +7689,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="202">
         <v>42</v>
       </c>
@@ -7645,7 +7715,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="202">
         <v>42</v>
       </c>
@@ -7671,7 +7741,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="199">
         <v>43</v>
       </c>
@@ -7697,7 +7767,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="199">
         <v>43</v>
       </c>
@@ -7723,7 +7793,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="199">
         <v>43</v>
       </c>
@@ -7749,7 +7819,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="202">
         <v>44</v>
       </c>
@@ -7775,7 +7845,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="202">
         <v>44</v>
       </c>
@@ -7801,7 +7871,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="202">
         <v>44</v>
       </c>
@@ -7827,7 +7897,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="199">
         <v>45</v>
       </c>
@@ -7853,7 +7923,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="199">
         <v>45</v>
       </c>
@@ -7879,7 +7949,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="199">
         <v>45</v>
       </c>
@@ -7905,7 +7975,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="199">
         <v>45</v>
       </c>
@@ -7931,7 +8001,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="202">
         <v>46</v>
       </c>
@@ -7955,7 +8025,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="202">
         <v>46</v>
       </c>
@@ -7979,7 +8049,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="202">
         <v>46</v>
       </c>
@@ -8003,7 +8073,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="202">
         <v>46</v>
       </c>
@@ -8027,7 +8097,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="199">
         <v>47</v>
       </c>
@@ -8053,7 +8123,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="199">
         <v>47</v>
       </c>
@@ -8079,7 +8149,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="199">
         <v>47</v>
       </c>
@@ -8105,7 +8175,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="199">
         <v>47</v>
       </c>
@@ -8131,7 +8201,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="202">
         <v>48</v>
       </c>
@@ -8157,7 +8227,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="202">
         <v>48</v>
       </c>
@@ -8183,7 +8253,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="202">
         <v>48</v>
       </c>
@@ -8209,7 +8279,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="202">
         <v>48</v>
       </c>
@@ -8235,9 +8305,9 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B171" s="198" t="s">
         <v>182</v>
@@ -8260,9 +8330,9 @@
         <v>960</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B172" s="198" t="s">
         <v>153</v>
@@ -8285,9 +8355,9 @@
         <v>855</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B173" s="198" t="s">
         <v>154</v>
@@ -8310,9 +8380,9 @@
         <v>855</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="250" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B174" s="201" t="s">
         <v>157</v>
@@ -8335,9 +8405,9 @@
         <v>672</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="250" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B175" s="201" t="s">
         <v>158</v>
@@ -8360,9 +8430,9 @@
         <v>684</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="250" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B176" s="201" t="s">
         <v>159</v>
@@ -8385,9 +8455,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="250" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B177" s="201" t="s">
         <v>160</v>
@@ -8410,9 +8480,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B178" s="198" t="s">
         <v>161</v>
@@ -8435,9 +8505,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B179" s="198" t="s">
         <v>162</v>
@@ -8460,9 +8530,9 @@
         <v>525</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B180" s="198" t="s">
         <v>163</v>
@@ -8485,9 +8555,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B181" s="198" t="s">
         <v>164</v>
@@ -8510,9 +8580,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B182" s="198" t="s">
         <v>165</v>
@@ -8535,9 +8605,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="107" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B183" s="198" t="s">
         <v>166</v>
@@ -8560,9 +8630,9 @@
         <v>450</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="250" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B184" s="201" t="s">
         <v>159</v>
@@ -8585,9 +8655,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="250" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B185" s="201" t="s">
         <v>160</v>
@@ -8610,9 +8680,9 @@
         <v>390</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="250" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B186" s="201" t="s">
         <v>162</v>
@@ -8635,9 +8705,9 @@
         <v>945</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="107" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B187" s="198" t="s">
         <v>157</v>
@@ -8660,9 +8730,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="107" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B188" s="198" t="s">
         <v>158</v>
@@ -8685,9 +8755,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="107" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B189" s="198" t="s">
         <v>167</v>
@@ -8710,9 +8780,9 @@
         <v>603</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="107" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B190" s="198" t="s">
         <v>169</v>
@@ -8735,9 +8805,9 @@
         <v>603</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="250" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B191" s="201" t="s">
         <v>182</v>
@@ -8760,9 +8830,9 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="250" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B192" s="201" t="s">
         <v>170</v>
@@ -8785,9 +8855,9 @@
         <v>840</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="250" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B193" s="201" t="s">
         <v>168</v>
@@ -8810,9 +8880,9 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="107" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B194" s="198" t="s">
         <v>162</v>
@@ -8835,9 +8905,9 @@
         <v>630</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="107" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B195" s="198" t="s">
         <v>166</v>
@@ -8860,9 +8930,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="250" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B196" s="201" t="s">
         <v>161</v>
@@ -8885,9 +8955,9 @@
         <v>710</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="250" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B197" s="201" t="s">
         <v>165</v>
@@ -8910,9 +8980,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="250" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B198" s="201" t="s">
         <v>166</v>
@@ -8935,9 +9005,9 @@
         <v>780</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="107" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B199" s="198" t="s">
         <v>182</v>
@@ -8960,9 +9030,9 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="107" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B200" s="198" t="s">
         <v>153</v>
@@ -8985,9 +9055,9 @@
         <v>330</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="107" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B201" s="198" t="s">
         <v>154</v>
@@ -9010,9 +9080,9 @@
         <v>324</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="250" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B202" s="201" t="s">
         <v>157</v>
@@ -9035,9 +9105,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="250" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B203" s="201" t="s">
         <v>158</v>
@@ -9060,9 +9130,9 @@
         <v>660</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="250" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B204" s="201" t="s">
         <v>159</v>
@@ -9085,9 +9155,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="250" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B205" s="201" t="s">
         <v>160</v>
@@ -9110,9 +9180,9 @@
         <v>318</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B206" s="198" t="s">
         <v>159</v>
@@ -9135,9 +9205,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B207" s="198" t="s">
         <v>160</v>
@@ -9160,9 +9230,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B208" s="198" t="s">
         <v>163</v>
@@ -9185,9 +9255,9 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B209" s="198" t="s">
         <v>164</v>
@@ -9210,9 +9280,9 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="250" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B210" s="201" t="s">
         <v>167</v>
@@ -9235,9 +9305,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="250" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B211" s="201" t="s">
         <v>169</v>
@@ -9260,9 +9330,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="250" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B212" s="201" t="s">
         <v>170</v>
@@ -9285,9 +9355,9 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="250" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B213" s="201" t="s">
         <v>168</v>
@@ -9310,9 +9380,9 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="107" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B214" s="198" t="s">
         <v>157</v>
@@ -9335,9 +9405,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="107" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B215" s="198" t="s">
         <v>158</v>
@@ -9360,9 +9430,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="107" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B216" s="198" t="s">
         <v>170</v>
@@ -9385,9 +9455,9 @@
         <v>490</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="107" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B217" s="198" t="s">
         <v>168</v>
@@ -9410,9 +9480,9 @@
         <v>490</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="250" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B218" s="201" t="s">
         <v>159</v>
@@ -9435,9 +9505,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="250" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B219" s="201" t="s">
         <v>160</v>
@@ -9460,9 +9530,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="250" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B220" s="201" t="s">
         <v>165</v>
@@ -9485,9 +9555,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="250" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B221" s="201" t="s">
         <v>166</v>
@@ -9510,9 +9580,9 @@
         <v>792</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B222" s="198" t="s">
         <v>182</v>
@@ -9535,9 +9605,9 @@
         <v>800</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B223" s="198" t="s">
         <v>170</v>
@@ -9560,9 +9630,9 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B224" s="198" t="s">
         <v>168</v>
@@ -9594,21 +9664,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="57.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" style="144" customWidth="1"/>
-    <col min="4" max="4" width="56.21875" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="57.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="144" customWidth="1"/>
+    <col min="4" max="4" width="56.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" style="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="184" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="184" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="186" t="s">
         <v>171</v>
       </c>
@@ -9637,7 +9707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="154" t="s">
         <v>173</v>
       </c>
@@ -9683,7 +9753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="156" t="s">
         <v>173</v>
       </c>
@@ -9725,7 +9795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="158" t="s">
         <v>177</v>
       </c>
@@ -9767,7 +9837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="158" t="s">
         <v>177</v>
       </c>
@@ -9808,7 +9878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="159" t="s">
         <v>184</v>
       </c>
@@ -9851,7 +9921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="159" t="s">
         <v>184</v>
       </c>
@@ -9893,7 +9963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="159" t="s">
         <v>184</v>
       </c>
@@ -9936,7 +10006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="159" t="s">
         <v>184</v>
       </c>
@@ -9979,7 +10049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="159" t="s">
         <v>184</v>
       </c>
@@ -10022,7 +10092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="161" t="s">
         <v>172</v>
       </c>
@@ -10065,7 +10135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="161" t="s">
         <v>172</v>
       </c>
@@ -10108,7 +10178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="163" t="s">
         <v>172</v>
       </c>
@@ -10140,7 +10210,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="165" t="s">
         <v>172</v>
       </c>
@@ -10172,7 +10242,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="161" t="s">
         <v>172</v>
       </c>
@@ -10204,7 +10274,7 @@
         <v>19, 20</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="163" t="s">
         <v>172</v>
       </c>
@@ -10236,7 +10306,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="167" t="s">
         <v>172</v>
       </c>
@@ -10268,7 +10338,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="169" t="s">
         <v>172</v>
       </c>
@@ -10300,7 +10370,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="165" t="s">
         <v>172</v>
       </c>
@@ -10332,7 +10402,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="163" t="s">
         <v>172</v>
       </c>
@@ -10364,7 +10434,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="165" t="s">
         <v>172</v>
       </c>
@@ -10396,7 +10466,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="161" t="s">
         <v>172</v>
       </c>
@@ -10428,7 +10498,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="161" t="s">
         <v>172</v>
       </c>
@@ -10460,7 +10530,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="161" t="s">
         <v>172</v>
       </c>
@@ -10492,7 +10562,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="161" t="s">
         <v>172</v>
       </c>
@@ -10524,7 +10594,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="169" t="s">
         <v>172</v>
       </c>
@@ -10556,7 +10626,7 @@
         <v>28, 29, 30</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="165" t="s">
         <v>172</v>
       </c>
@@ -10588,7 +10658,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="161" t="s">
         <v>172</v>
       </c>
@@ -10620,7 +10690,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="161" t="s">
         <v>172</v>
       </c>
@@ -10652,7 +10722,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="161" t="s">
         <v>172</v>
       </c>
@@ -10684,7 +10754,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="161" t="s">
         <v>172</v>
       </c>
@@ -10716,7 +10786,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="163" t="s">
         <v>172</v>
       </c>
@@ -10748,7 +10818,7 @@
         <v>28, 29, 30</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="167" t="s">
         <v>172</v>
       </c>
@@ -10780,7 +10850,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="161" t="s">
         <v>172</v>
       </c>
@@ -10812,7 +10882,7 @@
         <v>19, 20</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="169" t="s">
         <v>172</v>
       </c>
@@ -10844,7 +10914,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="165" t="s">
         <v>172</v>
       </c>
@@ -10876,7 +10946,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="161" t="s">
         <v>172</v>
       </c>
@@ -10908,7 +10978,7 @@
         <v>19, 20</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="163" t="s">
         <v>172</v>
       </c>
@@ -10940,7 +11010,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="167" t="s">
         <v>172</v>
       </c>
@@ -10972,7 +11042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="169" t="s">
         <v>172</v>
       </c>
@@ -11004,7 +11074,7 @@
         <v>19, 20</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="165" t="s">
         <v>172</v>
       </c>
@@ -11036,7 +11106,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="161" t="s">
         <v>172</v>
       </c>
@@ -11068,7 +11138,7 @@
         <v>19, 20</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="161" t="s">
         <v>172</v>
       </c>
@@ -11100,7 +11170,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="161" t="s">
         <v>172</v>
       </c>
@@ -11132,7 +11202,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="161" t="s">
         <v>172</v>
       </c>
@@ -11164,7 +11234,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="161" t="s">
         <v>172</v>
       </c>
@@ -11196,7 +11266,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="163" t="s">
         <v>172</v>
       </c>
@@ -11228,7 +11298,7 @@
         <v>28, 29, 30</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="167" t="s">
         <v>172</v>
       </c>
@@ -11260,7 +11330,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="161" t="s">
         <v>172</v>
       </c>
@@ -11292,7 +11362,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="169" t="s">
         <v>172</v>
       </c>
@@ -11324,7 +11394,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="165" t="s">
         <v>172</v>
       </c>
@@ -11356,7 +11426,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="161" t="s">
         <v>172</v>
       </c>
@@ -11388,7 +11458,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="163" t="s">
         <v>172</v>
       </c>
@@ -11420,7 +11490,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="167" t="s">
         <v>172</v>
       </c>
@@ -11452,7 +11522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="169" t="s">
         <v>172</v>
       </c>
@@ -11484,7 +11554,7 @@
         <v>17, 18</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="165" t="s">
         <v>172</v>
       </c>
@@ -11516,7 +11586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="161" t="s">
         <v>172</v>
       </c>
@@ -11548,7 +11618,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="161" t="s">
         <v>172</v>
       </c>
@@ -11580,7 +11650,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="161" t="s">
         <v>172</v>
       </c>
@@ -11612,7 +11682,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="161" t="s">
         <v>172</v>
       </c>
@@ -11644,7 +11714,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="163" t="s">
         <v>172</v>
       </c>
@@ -11676,7 +11746,7 @@
         <v>28, 29, 30</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="167" t="s">
         <v>172</v>
       </c>
@@ -11708,7 +11778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="161" t="s">
         <v>172</v>
       </c>
@@ -11740,7 +11810,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="163" t="s">
         <v>172</v>
       </c>
@@ -11772,7 +11842,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="165" t="s">
         <v>172</v>
       </c>
@@ -11804,7 +11874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="161" t="s">
         <v>172</v>
       </c>
@@ -11836,7 +11906,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="169" t="s">
         <v>172</v>
       </c>
@@ -11868,7 +11938,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="165" t="s">
         <v>172</v>
       </c>
@@ -11900,7 +11970,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="161" t="s">
         <v>172</v>
       </c>
@@ -11932,7 +12002,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="161" t="s">
         <v>172</v>
       </c>
@@ -11964,7 +12034,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="161" t="s">
         <v>172</v>
       </c>
@@ -11996,7 +12066,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="161" t="s">
         <v>172</v>
       </c>
@@ -12028,7 +12098,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="161" t="s">
         <v>172</v>
       </c>
@@ -12060,7 +12130,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="163" t="s">
         <v>172</v>
       </c>
@@ -12092,7 +12162,7 @@
         <v>28, 29, 30</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="167" t="s">
         <v>172</v>
       </c>
@@ -12124,7 +12194,7 @@
         <v>2, 3</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="161" t="s">
         <v>172</v>
       </c>
@@ -12156,7 +12226,7 @@
         <v>14, 15, 16</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="161" t="s">
         <v>172</v>
       </c>
@@ -12188,7 +12258,7 @@
         <v>5, 6, 7, 8, 9, 10, 11, 12, 13</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="161" t="s">
         <v>172</v>
       </c>
@@ -12220,7 +12290,7 @@
         <v>21, 22</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="161" t="s">
         <v>172</v>
       </c>
@@ -12252,7 +12322,7 @@
         <v>23, 24, 25</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="161" t="s">
         <v>172</v>
       </c>
@@ -12284,7 +12354,7 @@
         <v>26, 27</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="163" t="s">
         <v>172</v>
       </c>
@@ -12328,21 +12398,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H247"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="87" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="87" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="87" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" style="87" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="90" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="87" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="87" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="87" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="87" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="90" customWidth="1"/>
     <col min="6" max="6" width="16" style="87" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" style="87" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="87" customWidth="1"/>
-    <col min="9" max="10" width="8.88671875" style="87" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="87"/>
+    <col min="7" max="7" width="15.5703125" style="87" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="87" customWidth="1"/>
+    <col min="9" max="10" width="8.85546875" style="87" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="87"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
@@ -12368,7 +12438,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="64">
         <v>2</v>
       </c>
@@ -12395,7 +12465,7 @@
         <v>1.1111111111111072E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
         <v>2</v>
       </c>
@@ -12422,7 +12492,7 @@
         <v>4.0277777777777801E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="64">
         <v>2</v>
       </c>
@@ -12449,7 +12519,7 @@
         <v>2.430555555555558E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="64">
         <v>2</v>
       </c>
@@ -12476,7 +12546,7 @@
         <v>3.1944444444444386E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="64">
         <v>2</v>
       </c>
@@ -12503,7 +12573,7 @@
         <v>4.8611111111111105E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="64">
         <v>2</v>
       </c>
@@ -12530,7 +12600,7 @@
         <v>6.9444444444444198E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="64">
         <v>2</v>
       </c>
@@ -12557,7 +12627,7 @@
         <v>3.7500000000000033E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="64">
         <v>2</v>
       </c>
@@ -12584,7 +12654,7 @@
         <v>2.5694444444444409E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="64">
         <v>2</v>
       </c>
@@ -12611,7 +12681,7 @@
         <v>6.0416666666666674E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="64">
         <v>2</v>
       </c>
@@ -12638,7 +12708,7 @@
         <v>1.2499999999999956E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="64">
         <v>2</v>
       </c>
@@ -12665,7 +12735,7 @@
         <v>1.736111111111116E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="64">
         <v>2</v>
       </c>
@@ -12692,7 +12762,7 @@
         <v>1.2500000000000011E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="64">
         <v>2</v>
       </c>
@@ -12719,7 +12789,7 @@
         <v>8.4027777777777812E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="64">
         <v>2</v>
       </c>
@@ -12746,7 +12816,7 @@
         <v>2.7083333333333293E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="64">
         <v>2</v>
       </c>
@@ -12773,7 +12843,7 @@
         <v>1.736111111111116E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="64">
         <v>2</v>
       </c>
@@ -12800,7 +12870,7 @@
         <v>1.1805555555555514E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="64">
         <v>2</v>
       </c>
@@ -12827,7 +12897,7 @@
         <v>0.10277777777777775</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="64">
         <v>2</v>
       </c>
@@ -12854,7 +12924,7 @@
         <v>1.1805555555555458E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="64">
         <v>2</v>
       </c>
@@ -12881,7 +12951,7 @@
         <v>1.9444444444444486E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="64">
         <v>2</v>
       </c>
@@ -12908,7 +12978,7 @@
         <v>1.87500000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="64">
         <v>2</v>
       </c>
@@ -12935,7 +13005,7 @@
         <v>3.1944444444444497E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="64">
         <v>2</v>
       </c>
@@ -12962,7 +13032,7 @@
         <v>2.430555555555558E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="64">
         <v>2</v>
       </c>
@@ -12989,7 +13059,7 @@
         <v>1.0416666666666741E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="65">
         <v>2</v>
       </c>
@@ -13016,7 +13086,7 @@
         <v>2.916666666666673E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="64">
         <v>4</v>
       </c>
@@ -13043,7 +13113,7 @@
         <v>1.1111111111111072E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="64">
         <v>4</v>
       </c>
@@ -13070,7 +13140,7 @@
         <v>4.0277777777777801E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="64">
         <v>4</v>
       </c>
@@ -13097,7 +13167,7 @@
         <v>2.430555555555558E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="64">
         <v>4</v>
       </c>
@@ -13124,7 +13194,7 @@
         <v>3.1944444444444386E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="64">
         <v>4</v>
       </c>
@@ -13151,7 +13221,7 @@
         <v>4.8611111111111105E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="64">
         <v>4</v>
       </c>
@@ -13178,7 +13248,7 @@
         <v>6.9444444444444198E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="64">
         <v>4</v>
       </c>
@@ -13205,7 +13275,7 @@
         <v>3.7500000000000033E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="64">
         <v>4</v>
       </c>
@@ -13232,7 +13302,7 @@
         <v>2.5694444444444409E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="64">
         <v>4</v>
       </c>
@@ -13259,7 +13329,7 @@
         <v>6.0416666666666674E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="64">
         <v>4</v>
       </c>
@@ -13286,7 +13356,7 @@
         <v>1.2499999999999956E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="64">
         <v>4</v>
       </c>
@@ -13313,7 +13383,7 @@
         <v>1.736111111111116E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="64">
         <v>4</v>
       </c>
@@ -13340,7 +13410,7 @@
         <v>1.2500000000000011E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="64">
         <v>4</v>
       </c>
@@ -13367,7 +13437,7 @@
         <v>8.4027777777777812E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="64">
         <v>4</v>
       </c>
@@ -13394,7 +13464,7 @@
         <v>2.7083333333333293E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="64">
         <v>4</v>
       </c>
@@ -13421,7 +13491,7 @@
         <v>1.736111111111116E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="64">
         <v>4</v>
       </c>
@@ -13448,7 +13518,7 @@
         <v>1.1805555555555514E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="64">
         <v>4</v>
       </c>
@@ -13475,7 +13545,7 @@
         <v>0.10277777777777775</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="64">
         <v>4</v>
       </c>
@@ -13502,7 +13572,7 @@
         <v>1.1805555555555458E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="64">
         <v>4</v>
       </c>
@@ -13529,7 +13599,7 @@
         <v>1.9444444444444486E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="64">
         <v>4</v>
       </c>
@@ -13556,7 +13626,7 @@
         <v>1.87500000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="64">
         <v>4</v>
       </c>
@@ -13583,7 +13653,7 @@
         <v>3.1944444444444497E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="64">
         <v>4</v>
       </c>
@@ -13610,7 +13680,7 @@
         <v>2.430555555555558E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="64">
         <v>4</v>
       </c>
@@ -13637,7 +13707,7 @@
         <v>1.0416666666666741E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="64">
         <v>4</v>
       </c>
@@ -13664,7 +13734,7 @@
         <v>2.916666666666673E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="57">
         <v>5</v>
       </c>
@@ -13691,7 +13761,7 @@
         <v>7.7083333333333337E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="57">
         <v>5</v>
       </c>
@@ -13718,7 +13788,7 @@
         <v>9.7222222222222987E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="57">
         <v>5</v>
       </c>
@@ -13745,7 +13815,7 @@
         <v>6.1111111111111227E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="57">
         <v>5</v>
       </c>
@@ -13772,7 +13842,7 @@
         <v>2.8472222222222121E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="57">
         <v>5</v>
       </c>
@@ -13799,7 +13869,7 @@
         <v>9.7222222222221877E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="57">
         <v>5</v>
       </c>
@@ -13826,7 +13896,7 @@
         <v>2.9861111111111116E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="81">
         <v>5</v>
       </c>
@@ -13853,7 +13923,7 @@
         <v>6.944444444444442E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="98">
         <v>6</v>
       </c>
@@ -13880,7 +13950,7 @@
         <v>7.49999999999999E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="54">
         <v>6</v>
       </c>
@@ -13907,7 +13977,7 @@
         <v>1.3888888888888951E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="54">
         <v>6</v>
       </c>
@@ -13934,7 +14004,7 @@
         <v>1.2500000000000011E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="54">
         <v>6</v>
       </c>
@@ -13961,7 +14031,7 @@
         <v>5.9722222222222232E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="54">
         <v>6</v>
       </c>
@@ -13988,7 +14058,7 @@
         <v>5.6944444444444409E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="54">
         <v>6</v>
       </c>
@@ -14015,7 +14085,7 @@
         <v>6.5277777777777768E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="54">
         <v>6</v>
       </c>
@@ -14042,7 +14112,7 @@
         <v>1.5277777777777835E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="54">
         <v>6</v>
       </c>
@@ -14069,7 +14139,7 @@
         <v>1.5972222222222221E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="54">
         <v>6</v>
       </c>
@@ -14096,7 +14166,7 @@
         <v>7.1527777777777801E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="54">
         <v>6</v>
       </c>
@@ -14123,7 +14193,7 @@
         <v>7.6388888888889173E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="54">
         <v>6</v>
       </c>
@@ -14150,7 +14220,7 @@
         <v>1.3194444444444398E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="54">
         <v>6</v>
       </c>
@@ -14177,7 +14247,7 @@
         <v>4.5833333333333337E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="54">
         <v>6</v>
       </c>
@@ -14204,7 +14274,7 @@
         <v>3.8194444444444392E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="54">
         <v>6</v>
       </c>
@@ -14231,7 +14301,7 @@
         <v>9.0277777777777818E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="54">
         <v>6</v>
       </c>
@@ -14258,7 +14328,7 @@
         <v>4.2361111111111072E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="60">
         <v>6</v>
       </c>
@@ -14285,7 +14355,7 @@
         <v>4.5833333333333393E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="78">
         <v>7</v>
       </c>
@@ -14312,7 +14382,7 @@
         <v>3.5416666666666596E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="57">
         <v>7</v>
       </c>
@@ -14339,7 +14409,7 @@
         <v>1.5972222222222221E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="57">
         <v>7</v>
       </c>
@@ -14366,7 +14436,7 @@
         <v>6.1111111111111061E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="57">
         <v>7</v>
       </c>
@@ -14393,7 +14463,7 @@
         <v>1.5972222222222165E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="57">
         <v>7</v>
       </c>
@@ -14420,7 +14490,7 @@
         <v>2.916666666666673E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="57">
         <v>7</v>
       </c>
@@ -14447,7 +14517,7 @@
         <v>0.1159722222222222</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="57">
         <v>7</v>
       </c>
@@ -14474,7 +14544,7 @@
         <v>2.3611111111111138E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="57">
         <v>7</v>
       </c>
@@ -14501,7 +14571,7 @@
         <v>1.5972222222222221E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="57">
         <v>7</v>
       </c>
@@ -14528,7 +14598,7 @@
         <v>0.12222222222222223</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="57">
         <v>7</v>
       </c>
@@ -14555,7 +14625,7 @@
         <v>4.1666666666666741E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="57">
         <v>7</v>
       </c>
@@ -14582,7 +14652,7 @@
         <v>1.1111111111111072E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="57">
         <v>7</v>
       </c>
@@ -14609,7 +14679,7 @@
         <v>2.0833333333333426E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="57">
         <v>7</v>
       </c>
@@ -14636,7 +14706,7 @@
         <v>2.6388888888888906E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="57">
         <v>7</v>
       </c>
@@ -14663,7 +14733,7 @@
         <v>1.4583333333333282E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="57">
         <v>7</v>
       </c>
@@ -14690,7 +14760,7 @@
         <v>1.7361111111111105E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="57">
         <v>7</v>
       </c>
@@ -14717,7 +14787,7 @@
         <v>4.1666666666666519E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="57">
         <v>7</v>
       </c>
@@ -14744,7 +14814,7 @@
         <v>7.4999999999999956E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="112">
         <v>7</v>
       </c>
@@ -14771,7 +14841,7 @@
         <v>1.6666666666666607E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="98">
         <v>8</v>
       </c>
@@ -14798,7 +14868,7 @@
         <v>2.9861111111111227E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="54">
         <v>8</v>
       </c>
@@ -14825,7 +14895,7 @@
         <v>5.5555555555554803E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="54">
         <v>8</v>
       </c>
@@ -14852,7 +14922,7 @@
         <v>1.7361111111111049E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="54">
         <v>8</v>
       </c>
@@ -14879,7 +14949,7 @@
         <v>2.1527777777777812E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="54">
         <v>8</v>
       </c>
@@ -14906,7 +14976,7 @@
         <v>2.7777777777777679E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="54">
         <v>8</v>
       </c>
@@ -14933,7 +15003,7 @@
         <v>5.5555555555556468E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="54">
         <v>8</v>
       </c>
@@ -14960,7 +15030,7 @@
         <v>1.6666666666666607E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="54">
         <v>8</v>
       </c>
@@ -14987,7 +15057,7 @@
         <v>1.1805555555555514E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="54">
         <v>8</v>
       </c>
@@ -15014,7 +15084,7 @@
         <v>3.5416666666666652E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="54">
         <v>8</v>
       </c>
@@ -15041,7 +15111,7 @@
         <v>1.3888888888888895E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="54">
         <v>8</v>
       </c>
@@ -15068,7 +15138,7 @@
         <v>1.1111111111111072E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="54">
         <v>8</v>
       </c>
@@ -15095,7 +15165,7 @@
         <v>1.3194444444444509E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="54">
         <v>8</v>
       </c>
@@ -15122,7 +15192,7 @@
         <v>8.3333333333333037E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="54">
         <v>8</v>
       </c>
@@ -15149,7 +15219,7 @@
         <v>1.0416666666666741E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="54">
         <v>8</v>
       </c>
@@ -15176,7 +15246,7 @@
         <v>0.1020833333333333</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="54">
         <v>8</v>
       </c>
@@ -15203,7 +15273,7 @@
         <v>3.9583333333333304E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="54">
         <v>8</v>
       </c>
@@ -15230,7 +15300,7 @@
         <v>2.3611111111111194E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="54">
         <v>8</v>
       </c>
@@ -15257,7 +15327,7 @@
         <v>7.7777777777777835E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="54">
         <v>8</v>
       </c>
@@ -15284,7 +15354,7 @@
         <v>8.3333333333334147E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="54">
         <v>8</v>
       </c>
@@ -15311,7 +15381,7 @@
         <v>9.7222222222222987E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="54">
         <v>8</v>
       </c>
@@ -15338,7 +15408,7 @@
         <v>0.12291666666666667</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="60">
         <v>8</v>
       </c>
@@ -15365,7 +15435,7 @@
         <v>4.1666666666667074E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="78">
         <v>9</v>
       </c>
@@ -15392,7 +15462,7 @@
         <v>7.1527777777777801E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="57">
         <v>9</v>
       </c>
@@ -15419,7 +15489,7 @@
         <v>4.1666666666666685E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="57">
         <v>9</v>
       </c>
@@ -15446,7 +15516,7 @@
         <v>4.0972222222222299E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="57">
         <v>9</v>
       </c>
@@ -15473,7 +15543,7 @@
         <v>2.7777777777778234E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="57">
         <v>9</v>
       </c>
@@ -15500,7 +15570,7 @@
         <v>6.9444444444445308E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="57">
         <v>9</v>
       </c>
@@ -15527,7 +15597,7 @@
         <v>1.4583333333333282E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="57">
         <v>9</v>
       </c>
@@ -15554,7 +15624,7 @@
         <v>6.2500000000000333E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="57">
         <v>9</v>
       </c>
@@ -15581,7 +15651,7 @@
         <v>1.1805555555555569E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="57">
         <v>9</v>
       </c>
@@ -15608,7 +15678,7 @@
         <v>1.0416666666666741E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="57">
         <v>9</v>
       </c>
@@ -15635,7 +15705,7 @@
         <v>5.5555555555555358E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="57">
         <v>9</v>
       </c>
@@ -15662,7 +15732,7 @@
         <v>7.0138888888888862E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="57">
         <v>9</v>
       </c>
@@ -15689,7 +15759,7 @@
         <v>8.6111111111111194E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="57">
         <v>9</v>
       </c>
@@ -15716,7 +15786,7 @@
         <v>7.6388888888888618E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="57">
         <v>9</v>
       </c>
@@ -15743,7 +15813,7 @@
         <v>2.8472222222222232E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="57">
         <v>9</v>
       </c>
@@ -15770,7 +15840,7 @@
         <v>1.4583333333333393E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="57">
         <v>9</v>
       </c>
@@ -15797,7 +15867,7 @@
         <v>2.6388888888888906E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="57">
         <v>9</v>
       </c>
@@ -15824,7 +15894,7 @@
         <v>6.9444444444444531E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="81">
         <v>9</v>
       </c>
@@ -15851,7 +15921,7 @@
         <v>8.3333333333334147E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="54">
         <v>10</v>
       </c>
@@ -15878,7 +15948,7 @@
         <v>3.1944444444444442E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="54">
         <v>10</v>
       </c>
@@ -15905,7 +15975,7 @@
         <v>5.5555555555554803E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="54">
         <v>10</v>
       </c>
@@ -15932,7 +16002,7 @@
         <v>3.1944444444444442E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="54">
         <v>10</v>
       </c>
@@ -15959,7 +16029,7 @@
         <v>2.0138888888888817E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="54">
         <v>10</v>
       </c>
@@ -15986,7 +16056,7 @@
         <v>0.10347222222222224</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="54">
         <v>10</v>
       </c>
@@ -16013,7 +16083,7 @@
         <v>3.6111111111111094E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="54">
         <v>10</v>
       </c>
@@ -16040,7 +16110,7 @@
         <v>7.4999999999999956E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="54">
         <v>10</v>
       </c>
@@ -16067,7 +16137,7 @@
         <v>3.6111111111111149E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="54">
         <v>10</v>
       </c>
@@ -16094,7 +16164,7 @@
         <v>4.8611111111110938E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="54">
         <v>10</v>
       </c>
@@ -16121,7 +16191,7 @@
         <v>2.7777777777777679E-3</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="54">
         <v>10</v>
       </c>
@@ -16148,7 +16218,7 @@
         <v>4.8611111111110938E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="54">
         <v>10</v>
       </c>
@@ -16175,7 +16245,7 @@
         <v>3.4722222222222099E-3</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="54">
         <v>10</v>
       </c>
@@ -16202,7 +16272,7 @@
         <v>4.1666666666667074E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="54">
         <v>10</v>
       </c>
@@ -16229,7 +16299,7 @@
         <v>9.7222222222221877E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="54">
         <v>10</v>
       </c>
@@ -16256,7 +16326,7 @@
         <v>3.0555555555555558E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="54">
         <v>10</v>
       </c>
@@ -16283,7 +16353,7 @@
         <v>5.347222222222231E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="54">
         <v>10</v>
       </c>
@@ -16310,7 +16380,7 @@
         <v>6.736111111111108E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="54">
         <v>10</v>
       </c>
@@ -16337,7 +16407,7 @@
         <v>3.6805555555555564E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="54">
         <v>10</v>
       </c>
@@ -16364,7 +16434,7 @@
         <v>1.3888888888888951E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="54">
         <v>10</v>
       </c>
@@ -16391,7 +16461,7 @@
         <v>7.6388888888888895E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="54">
         <v>10</v>
       </c>
@@ -16418,7 +16488,7 @@
         <v>2.2222222222222143E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="78">
         <v>11</v>
       </c>
@@ -16445,7 +16515,7 @@
         <v>0.10347222222222219</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="57">
         <v>11</v>
       </c>
@@ -16472,7 +16542,7 @@
         <v>1.5972222222222165E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="57">
         <v>11</v>
       </c>
@@ -16499,7 +16569,7 @@
         <v>5.0694444444444486E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="57">
         <v>11</v>
       </c>
@@ -16526,7 +16596,7 @@
         <v>2.7777777777776569E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="57">
         <v>11</v>
       </c>
@@ -16553,7 +16623,7 @@
         <v>7.6388888888888618E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="57">
         <v>11</v>
       </c>
@@ -16580,7 +16650,7 @@
         <v>2.5694444444444464E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="57">
         <v>11</v>
       </c>
@@ -16607,7 +16677,7 @@
         <v>6.9444444444444753E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="57">
         <v>11</v>
       </c>
@@ -16634,7 +16704,7 @@
         <v>2.0833333333333426E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="57">
         <v>11</v>
       </c>
@@ -16661,7 +16731,7 @@
         <v>5.8333333333333348E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="57">
         <v>11</v>
       </c>
@@ -16688,7 +16758,7 @@
         <v>6.0416666666666674E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="57">
         <v>11</v>
       </c>
@@ -16715,7 +16785,7 @@
         <v>5.5555555555556468E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="57">
         <v>11</v>
       </c>
@@ -16742,7 +16812,7 @@
         <v>1.388888888888884E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="57">
         <v>11</v>
       </c>
@@ -16769,7 +16839,7 @@
         <v>5.5555555555555358E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="57">
         <v>11</v>
       </c>
@@ -16796,7 +16866,7 @@
         <v>2.7777777777777679E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="57">
         <v>11</v>
       </c>
@@ -16823,7 +16893,7 @@
         <v>1.2500000000000122E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="57">
         <v>11</v>
       </c>
@@ -16850,7 +16920,7 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="57">
         <v>11</v>
       </c>
@@ -16877,7 +16947,7 @@
         <v>1.5972222222222165E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="57">
         <v>11</v>
       </c>
@@ -16904,7 +16974,7 @@
         <v>5.5555555555555358E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="57">
         <v>11</v>
       </c>
@@ -16931,7 +17001,7 @@
         <v>9.7222222222222987E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="57">
         <v>11</v>
       </c>
@@ -16958,7 +17028,7 @@
         <v>1.5277777777777835E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="57">
         <v>11</v>
       </c>
@@ -16985,7 +17055,7 @@
         <v>2.1527777777777812E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="57">
         <v>11</v>
       </c>
@@ -17012,7 +17082,7 @@
         <v>6.3888888888888884E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="57">
         <v>11</v>
       </c>
@@ -17039,7 +17109,7 @@
         <v>2.5694444444444464E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="57">
         <v>11</v>
       </c>
@@ -17066,7 +17136,7 @@
         <v>4.513888888888884E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="57">
         <v>11</v>
       </c>
@@ -17093,7 +17163,7 @@
         <v>1.8750000000000044E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="57">
         <v>11</v>
       </c>
@@ -17120,7 +17190,7 @@
         <v>3.1944444444444497E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="57">
         <v>11</v>
       </c>
@@ -17147,7 +17217,7 @@
         <v>4.1666666666666519E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="57">
         <v>11</v>
       </c>
@@ -17174,7 +17244,7 @@
         <v>5.208333333333337E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="57">
         <v>11</v>
       </c>
@@ -17201,7 +17271,7 @@
         <v>1.3194444444444398E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="112">
         <v>11</v>
       </c>
@@ -17228,7 +17298,7 @@
         <v>1.7361111111111216E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="98">
         <v>12</v>
       </c>
@@ -17255,7 +17325,7 @@
         <v>2.7083333333333404E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="54">
         <v>12</v>
       </c>
@@ -17282,7 +17352,7 @@
         <v>9.0277777777777457E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="54">
         <v>12</v>
       </c>
@@ -17309,7 +17379,7 @@
         <v>1.9444444444444375E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="54">
         <v>12</v>
       </c>
@@ -17336,7 +17406,7 @@
         <v>8.2638888888888873E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="54">
         <v>12</v>
       </c>
@@ -17363,7 +17433,7 @@
         <v>5.6250000000000022E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="54">
         <v>12</v>
       </c>
@@ -17390,7 +17460,7 @@
         <v>5.1388888888888928E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="54">
         <v>12</v>
       </c>
@@ -17417,7 +17487,7 @@
         <v>1.3194444444444398E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="54">
         <v>12</v>
       </c>
@@ -17444,7 +17514,7 @@
         <v>4.5833333333333393E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="54">
         <v>12</v>
       </c>
@@ -17471,7 +17541,7 @@
         <v>4.9999999999999989E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="54">
         <v>12</v>
       </c>
@@ -17498,7 +17568,7 @@
         <v>2.3611111111111138E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="54">
         <v>12</v>
       </c>
@@ -17525,7 +17595,7 @@
         <v>9.0277777777777457E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="54">
         <v>12</v>
       </c>
@@ -17552,7 +17622,7 @@
         <v>3.8194444444444364E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="54">
         <v>12</v>
       </c>
@@ -17579,7 +17649,7 @@
         <v>1.041666666666663E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="54">
         <v>12</v>
       </c>
@@ -17606,7 +17676,7 @@
         <v>7.6388888888888951E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="54">
         <v>12</v>
       </c>
@@ -17633,7 +17703,7 @@
         <v>1.3888888888888895E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="54">
         <v>12</v>
       </c>
@@ -17660,7 +17730,7 @@
         <v>5.6249999999999911E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="60">
         <v>12</v>
       </c>
@@ -17687,7 +17757,7 @@
         <v>1.2500000000000067E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="123">
         <v>13</v>
       </c>
@@ -17714,7 +17784,7 @@
         <v>2.4305555555555469E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="57">
         <v>13</v>
       </c>
@@ -17741,7 +17811,7 @@
         <v>5.6944444444444464E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="57">
         <v>13</v>
       </c>
@@ -17768,7 +17838,7 @@
         <v>3.6111111111111094E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="57">
         <v>13</v>
       </c>
@@ -17795,7 +17865,7 @@
         <v>2.222222222222231E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="57">
         <v>13</v>
       </c>
@@ -17822,7 +17892,7 @@
         <v>1.6666666666666691E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="57">
         <v>13</v>
       </c>
@@ -17849,7 +17919,7 @@
         <v>3.3333333333333326E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="57">
         <v>13</v>
       </c>
@@ -17876,7 +17946,7 @@
         <v>1.5972222222222276E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="57">
         <v>13</v>
       </c>
@@ -17903,7 +17973,7 @@
         <v>3.0555555555555558E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="57">
         <v>13</v>
       </c>
@@ -17930,7 +18000,7 @@
         <v>4.6527777777777835E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="57">
         <v>13</v>
       </c>
@@ -17957,7 +18027,7 @@
         <v>5.9722222222222315E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="57">
         <v>13</v>
       </c>
@@ -17984,7 +18054,7 @@
         <v>1.1805555555555625E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="57">
         <v>13</v>
       </c>
@@ -18011,7 +18081,7 @@
         <v>5.4861111111111027E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="57">
         <v>13</v>
       </c>
@@ -18038,7 +18108,7 @@
         <v>6.9444444444445308E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="57">
         <v>13</v>
       </c>
@@ -18065,7 +18135,7 @@
         <v>6.9444444444444198E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="57">
         <v>13</v>
       </c>
@@ -18092,7 +18162,7 @@
         <v>2.0833333333333259E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="57">
         <v>13</v>
       </c>
@@ -18119,7 +18189,7 @@
         <v>1.5277777777777724E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="57">
         <v>13</v>
       </c>
@@ -18146,7 +18216,7 @@
         <v>1.3888888888888895E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="57">
         <v>13</v>
       </c>
@@ -18173,7 +18243,7 @@
         <v>4.0277777777777801E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="57">
         <v>13</v>
       </c>
@@ -18200,7 +18270,7 @@
         <v>6.9444444444443643E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="57">
         <v>13</v>
       </c>
@@ -18227,7 +18297,7 @@
         <v>3.4027777777777782E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="112">
         <v>13</v>
       </c>
@@ -18254,7 +18324,7 @@
         <v>2.569444444444452E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="98">
         <v>17</v>
       </c>
@@ -18281,7 +18351,7 @@
         <v>1.8055555555555491E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="54">
         <v>17</v>
       </c>
@@ -18308,7 +18378,7 @@
         <v>3.9583333333333415E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="54">
         <v>17</v>
       </c>
@@ -18335,7 +18405,7 @@
         <v>5.5555555555556468E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="54">
         <v>17</v>
       </c>
@@ -18362,7 +18432,7 @@
         <v>0.1020833333333333</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="54">
         <v>17</v>
       </c>
@@ -18389,7 +18459,7 @@
         <v>5.1388888888888762E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="54">
         <v>17</v>
       </c>
@@ -18416,7 +18486,7 @@
         <v>7.9861111111111105E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="54">
         <v>17</v>
       </c>
@@ -18443,7 +18513,7 @@
         <v>6.9444444444444531E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="54">
         <v>17</v>
       </c>
@@ -18470,7 +18540,7 @@
         <v>3.9583333333333304E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="54">
         <v>17</v>
       </c>
@@ -18497,7 +18567,7 @@
         <v>7.1527777777777801E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="54">
         <v>17</v>
       </c>
@@ -18524,7 +18594,7 @@
         <v>3.0555555555555558E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="60">
         <v>17</v>
       </c>
@@ -18551,7 +18621,7 @@
         <v>1.7361111111111105E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="57">
         <v>18</v>
       </c>
@@ -18578,7 +18648,7 @@
         <v>9.6527777777777768E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="57">
         <v>18</v>
       </c>
@@ -18605,7 +18675,7 @@
         <v>2.2916666666666696E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="57">
         <v>18</v>
       </c>
@@ -18632,7 +18702,7 @@
         <v>5.9722222222222177E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="57">
         <v>18</v>
       </c>
@@ -18659,7 +18729,7 @@
         <v>2.5694444444444464E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="112">
         <v>18</v>
       </c>
@@ -18686,7 +18756,7 @@
         <v>8.3333333333333426E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="54">
         <v>19</v>
       </c>
@@ -18713,7 +18783,7 @@
         <v>5.4166666666666696E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="54">
         <v>19</v>
       </c>
@@ -18740,7 +18810,7 @@
         <v>1.1805555555555514E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="54">
         <v>19</v>
       </c>
@@ -18767,7 +18837,7 @@
         <v>2.3611111111111138E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="54">
         <v>19</v>
       </c>
@@ -18794,7 +18864,7 @@
         <v>2.2222222222222254E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="60">
         <v>19</v>
       </c>
@@ -18821,7 +18891,7 @@
         <v>2.8472222222222232E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="57">
         <v>20</v>
       </c>
@@ -18848,7 +18918,7 @@
         <v>0.1166666666666667</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="57">
         <v>20</v>
       </c>
@@ -18875,7 +18945,7 @@
         <v>0.10625000000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="57">
         <v>20</v>
       </c>
@@ -18902,7 +18972,7 @@
         <v>4.2361111111111127E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="112">
         <v>20</v>
       </c>
@@ -18929,7 +18999,7 @@
         <v>4.2361111111111127E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="98">
         <v>22</v>
       </c>
@@ -18956,7 +19026,7 @@
         <v>1.8749999999999933E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="54">
         <v>22</v>
       </c>
@@ -18983,7 +19053,7 @@
         <v>6.3194444444444442E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="60">
         <v>22</v>
       </c>
@@ -19023,16 +19093,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
@@ -19049,7 +19119,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="129">
         <v>2</v>
       </c>
@@ -19066,7 +19136,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="205">
         <v>4</v>
       </c>
@@ -19083,7 +19153,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>5</v>
       </c>
@@ -19100,7 +19170,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>6</v>
       </c>
@@ -19117,7 +19187,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>7</v>
       </c>
@@ -19134,7 +19204,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>8</v>
       </c>
@@ -19151,7 +19221,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>9</v>
       </c>
@@ -19168,7 +19238,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>10</v>
       </c>
@@ -19185,7 +19255,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>11</v>
       </c>
@@ -19202,7 +19272,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>12</v>
       </c>
@@ -19219,7 +19289,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>13</v>
       </c>
@@ -19236,7 +19306,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>17</v>
       </c>
@@ -19253,7 +19323,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>18</v>
       </c>
@@ -19270,7 +19340,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>19</v>
       </c>
@@ -19287,7 +19357,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>20</v>
       </c>
@@ -19304,7 +19374,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="129">
         <v>22</v>
       </c>
@@ -19329,19 +19399,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731E839A-0E28-4AA4-BC5E-59AF7764C5D7}">
   <dimension ref="B2:H29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="225"/>
-    <col min="2" max="2" width="17.88671875" style="225" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" style="225" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="225" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="225" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="225"/>
-    <col min="7" max="7" width="16.21875" style="225" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="225"/>
+    <col min="1" max="1" width="8.85546875" style="225"/>
+    <col min="2" max="2" width="17.85546875" style="225" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="225" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="225" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="225" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="225"/>
+    <col min="7" max="7" width="16.28515625" style="225" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="225"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" s="231" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" s="231" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B2" s="213" t="s">
         <v>186</v>
       </c>
@@ -19361,7 +19431,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="255" t="s">
         <v>191</v>
       </c>
@@ -19381,7 +19451,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="257"/>
       <c r="C4" s="233" t="s">
         <v>176</v>
@@ -19399,7 +19469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="252" t="s">
         <v>192</v>
       </c>
@@ -19419,7 +19489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="254"/>
       <c r="C6" s="230" t="s">
         <v>179</v>
@@ -19437,7 +19507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="255" t="s">
         <v>193</v>
       </c>
@@ -19457,7 +19527,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="257"/>
       <c r="C8" s="262"/>
       <c r="D8" s="259"/>
@@ -19471,7 +19541,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="257"/>
       <c r="C9" s="262"/>
       <c r="D9" s="259"/>
@@ -19485,7 +19555,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="257"/>
       <c r="C10" s="262"/>
       <c r="D10" s="259"/>
@@ -19499,7 +19569,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="256"/>
       <c r="C11" s="263"/>
       <c r="D11" s="260"/>
@@ -19513,15 +19583,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="195" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C13" s="195" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="195" t="s">
         <v>234</v>
-      </c>
-      <c r="D13" s="195" t="s">
-        <v>236</v>
       </c>
       <c r="G13" s="93" t="s">
         <v>6</v>
@@ -19530,9 +19600,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C14"/>
       <c r="G14" s="97" t="s">
@@ -19542,9 +19612,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C15"/>
       <c r="G15" s="97" t="s">
@@ -19554,9 +19624,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C16"/>
       <c r="G16" s="97" t="s">
@@ -19566,9 +19636,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C17"/>
       <c r="G17" s="97" t="s">
@@ -19578,9 +19648,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C18"/>
       <c r="G18" s="97" t="s">
@@ -19590,9 +19660,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C19"/>
       <c r="G19" s="97" t="s">
@@ -19602,9 +19672,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C20"/>
       <c r="G20" s="97" t="s">
@@ -19614,9 +19684,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C21"/>
       <c r="G21" s="97" t="s">
@@ -19626,9 +19696,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C22"/>
       <c r="G22" s="97" t="s">
@@ -19638,9 +19708,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C23"/>
       <c r="G23" s="97" t="s">
@@ -19650,9 +19720,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C24"/>
       <c r="G24" s="97" t="s">
@@ -19662,31 +19732,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>230</v>
       </c>
-      <c r="C25"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="C27"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>231</v>
       </c>
-      <c r="C26"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>232</v>
-      </c>
-      <c r="C27"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>233</v>
-      </c>
       <c r="C28"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29"/>
       <c r="C29"/>
     </row>
